--- a/_data_list/BTS-MAP FILE.xlsx
+++ b/_data_list/BTS-MAP FILE.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFA59BA-2FF7-46F3-8D68-5D3307D6BCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D715EF4-8212-48E3-9F68-ACECFF8D25ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="545" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="545" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="28" state="hidden" r:id="rId1"/>
@@ -11688,30 +11688,30 @@
   <dimension ref="A1:AA124"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" style="15" customWidth="1"/>
+    <col min="5" max="5" width="10" style="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" style="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="15" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" style="15" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.42578125" style="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" style="15" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="55.42578125" style="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="56.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="31.42578125" style="15" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="58.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="32.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
